--- a/jogos_2025-09-13.xlsx
+++ b/jogos_2025-09-13.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="M6" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1.64</v>
+        <v>3.13</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.06</v>
+        <v>3.5</v>
       </c>
       <c r="M8" t="n">
-        <v>10</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>19</v>
+        <v>1.98</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,16 +1482,16 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>3.13</v>
+        <v>4.3</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.51</v>
+        <v>1.06</v>
       </c>
       <c r="M10" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>6.1</v>
+        <v>19</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,16 +1740,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="M16" t="n">
         <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3252,10 +3252,10 @@
         <v>2.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.85</v>
+        <v>1.62</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="N31" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.85</v>
+        <v>2.85</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>4.1</v>
+        <v>2.45</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N43" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Penybont</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Penybont</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M51" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="N51" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Barry Town United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Barry Town United</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14118,16 +14118,16 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="M118" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N118" t="n">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15666,16 +15666,16 @@
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X118" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,49 +15762,49 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="M119" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N119" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y119" t="n">
         <v>1.9</v>
       </c>
-      <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="n">
-        <v>0</v>
-      </c>
-      <c r="T119" t="n">
-        <v>0</v>
-      </c>
-      <c r="U119" t="n">
-        <v>0</v>
-      </c>
-      <c r="V119" t="n">
-        <v>0</v>
-      </c>
-      <c r="W119" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y119" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Z119" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23019,10 +23019,10 @@
         <v>0</v>
       </c>
       <c r="W175" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X175" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y175" t="n">
         <v>0</v>
@@ -23373,13 +23373,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23406,10 +23406,10 @@
         <v>0</v>
       </c>
       <c r="W178" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X178" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y178" t="n">
         <v>0</v>
@@ -40014,13 +40014,13 @@
         </is>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M307" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N307" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O307" t="n">
         <v>0</v>
@@ -40401,13 +40401,13 @@
         </is>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M310" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N310" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O310" t="n">
         <v>0</v>
